--- a/synthetic_dirty_data.xlsx
+++ b/synthetic_dirty_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Plankton\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BD2E23-8422-4FF5-B6A4-6395EA400451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A14AA32-74AB-4C1D-A2E0-27770050D4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -67,7 +68,7 @@
     <t>wrong</t>
   </si>
   <si>
-    <t>abcmadachod</t>
+    <t>abc</t>
   </si>
 </sst>
 </file>
